--- a/Result/checksun_type/整車組裝、修理及技術服務.xlsx
+++ b/Result/checksun_type/整車組裝、修理及技術服務.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>35.61</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>36.04</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>33.85</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>10003939.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>16812721.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>16812721.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>28955598.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>37495260.14</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>37495260.14</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-4963789.006092828</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>10003939</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>10003939.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>35.49</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>33.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>16335914.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>24791136.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>24791136.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>29744586.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>37462800.8</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>37462800.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-4227662.37471519</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>16335914</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>16335914.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>35.94</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>36.29</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>33.43</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>33.43</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>11426356.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>28405642.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>28405642</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>30635525.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>37276453.84</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>37276453.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-3703490.852221593</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>11426356</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>11426356.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>36.5</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>33.23</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>33.23</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>23070340.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>40583749.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>40583749.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>31288459.2</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>37153017.02</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>37153017.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-2296382.789651394</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>23070340</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>23070340.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>33.05</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>23227058.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>39483592.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>39483592.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>32054656.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>36851291.98</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>36851291.98</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1451784.457777843</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>23227058</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>23227058.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>36.55</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>32.83</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>32.83</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>49896013.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>41098475.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>41098475.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>35111442.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>36487231.22</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>36487231.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-210157.1816092804</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>49896013</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>49896013.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>36.48</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>36.7</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>32.65</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>34408443.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>34698036.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>34698036.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>33253068.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>35584667.3</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>35584667.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1286286.352025293</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>34408443</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>34408443.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>35.92</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>32.41</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>32.41</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>72316895.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>32865409.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>32865409.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>37547059.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>35339260.36</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>35339260.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1118292.440047257</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>72316895</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>72316895.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>35.37</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>32.15</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>17569552.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>21993168.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>21993168.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>35485008.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>34069635.44</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>34069635.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-4899981.978648372</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>17569552</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>17569552.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>35.11</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>36.68</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>31.93</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>31301475.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>24625721.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>24625721</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>38550535.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>33946568.62</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>33946568.62</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-4261609.498841092</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>31301475</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>31301475.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>35.06</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>31.73</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>17893818.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>29124409.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>29124409.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>39927956.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>33607601.62</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>33607601.62</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-4668725.938443527</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>17893818</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>17893818.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>99.34</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>100.34</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>112.36</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>100.34</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>112.36</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>521125951.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>195257417.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>195257417.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>135411159.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>235068871.48</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>235068871.48</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>28699163.61055356</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>521125951</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>521125951.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>96.14</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>99.94</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>113.06</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>113.06</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>206818050.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>113088275.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>113088275.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>91558986.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>248796436.26</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>248796436.26</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-2054509.181443289</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>206818050</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>206818050.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>94.58</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>100.12</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>113.97</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>113.97</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>105558068.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>84064310.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>84064310.40000001</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>77278438.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>262913969.5</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>262913969.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-12239105.59210153</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>105558068</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>105558068.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>94.47999999999999</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>100.67</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>114.75</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>114.75</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>77701093.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>84340514.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>84340514.59999999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>80708581.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>275283597.96</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>275283597.96</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-15502134.3361811</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>77701093</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>77701093.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>95.94</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>101.52</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>115.7</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>101.52</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>115.7</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>65083925.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>76159188.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>76159188.59999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>84223161.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>289909826.8</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>289909826.8</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-16625280.42285976</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>65083925</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>65083925.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>97.3</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>102.38</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>116.42</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>102.38</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>116.42</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>110280242.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>75564902.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>75564902.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>85629356.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>321935517.76</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>321935517.76</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-16284175.3887271</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>110280242</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>110280242.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>98.6</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>103.28</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>117.09</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>103.28</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>117.09</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>61698224.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>70029696.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>70029696.40000001</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>100859230.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>330373425.72</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>330373425.72</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-20057767.32608305</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>61698224</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>61698224.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>99.42</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>104.18</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>117.57</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>117.57</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>106939089.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>70492567.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>70492567</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>148607606.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>338814767.18</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>338814767.18</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-19527047.90351717</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>106939089</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>106939089.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>100.2</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>105.12</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>117.82</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>105.12</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>117.82</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>36794463.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>77076648.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>77076648</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>149192678.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>347134252.82</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>347134252.82</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-22918718.26758315</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>36794463</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>36794463.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>100.24</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>106.11</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>118.02</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>106.11</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>118.02</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>62112493.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>92287134.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>92287134.59999999</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>149397987.1</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>354485332.7</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>354485332.7</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-19429940.34954941</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>62112493</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>62112493.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>100.94</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>106.96</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>118.17</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>106.96</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>118.17</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>82604213.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>95693810.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>95693810</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>149887175.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>364165058.36</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>364165058.36</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-16464691.52558875</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>82604213</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>82604213.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>56.36</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>54.55</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>54.94</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>54.94</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1557361.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1690822.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1690822</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>3508385.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2296716.04</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2296716.04</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-240310.4893460944</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1557361</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1557361.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>56.12</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>54.46</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>54.94</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>54.94</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1564020.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1831265.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1831265.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>3977462.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2291569.18</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2291569.18</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-181845.1023610453</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1564020</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1564020.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>55.92</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>54.97</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>54.97</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>2083050.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1971179.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1971179.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>3937273.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2302942.54</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>2302942.54</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-92542.11729808012</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2083050</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2083050.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>55.72000000000001</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>54.34</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>55.01</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>55.01</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1844728.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>2619148.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>2619148</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3844517.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2378408.26</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2378408.26</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-17271.70587605564</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1844728</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1844728.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>54.24</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>55.04</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>55.04</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1404951.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>4457110.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>4457110.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>3812701.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2401339.68</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2401339.68</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>116408.799936695</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1404951</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1404951.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>55.76000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>54.14</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>55.02</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>55.02</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>2259579.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>5325948.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>5325948.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3791943.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2382842.64</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2382842.64</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>350342.4582428858</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2259579</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2259579.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>54.08</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>55.03</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>55.03</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>2263591.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>6123659.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>6123659.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>3789897.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2372429.14</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>2372429.14</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>580453.8823144836</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>2263591</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>2263591.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>55.04</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>54.04</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>55.05</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>55.05</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>5322891.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>5903366.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>5903366.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>3780568.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2348035.54</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2348035.54</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>888024.1351912492</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>5322891</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>5322891.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>54.36</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>55.03</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>55.03</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>11034542.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>5069886.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>5069886.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>3421216.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2268506.2</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2268506.2</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>967912.920186941</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>11034542</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>11034542.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>53.4</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>53.81</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>54.99</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>53.81</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>54.99</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>5749141.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>3168292.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>3168292.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2677041.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2090171.28</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2090171.28</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>435508.8301741099</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>5749141</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>5749141.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>52.82000000000001</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>53.74</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>54.99</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>54.99</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>6248132.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>2257938.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>2257938.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2344082.7</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2009452.74</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2009452.74</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>225670.6362209907</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>6248132</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>6248132.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>61.62</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>61.27</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>61.76</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>61.76</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>27438023.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>28295127.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>28295127</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>48054814.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>43018314.76</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>43018314.76</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-3032782.225077435</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>27438023</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>27438023.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>61.36</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>61.18</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>61.79</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>61.79</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>20126832.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>27219730.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>27219730</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>48093438.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>44613807.02</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>44613807.02</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-2529493.454912305</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>20126832</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>20126832.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>61.26000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>61.14</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>61.88</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>61.88</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>42662624.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>34706537.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>34706537.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>48463333.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>45243312.38</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>45243312.38</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-936828.5527152494</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>42662624</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>42662624.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>61.4</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>61.1</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>61.97</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>61.97</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>30210284.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>42004980.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>42004980.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>47419499.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>44953330.72</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>44953330.72</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-1042683.958408192</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>30210284</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>30210284.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>61.92</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>62.09</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>62.09</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>21037872.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>68408887.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>68408887.40000001</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>46519228.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>45062406.52</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>45062406.52</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>177512.0319736078</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>21037872</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>21037872.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>61.85999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>61.19</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>62.19</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>62.19</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>22061038.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>67814502.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>67814502.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>49102358.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>45160380.1</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>45160380.1</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>2897067.874234259</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>22061038</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>22061038.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>61.85999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>61.18</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>62.3</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>62.3</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>57560870.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>68967146.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>68967146.40000001</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>51145979.9</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>45838398.06</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>45838398.06</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>6569056.010526821</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>57560870</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>57560870.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>61.77999999999999</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>61.15</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>62.37</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>62.37</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>79154837.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>62220128.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>62220128.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>49455209.0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>45194064.56</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>45194064.56</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>7776590.7762831</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>79154837</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>79154837.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>61.34</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>61.06</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>62.4</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>162229820.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>52834018.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>52834018.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>45005338.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>44159152.5</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>44159152.5</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>6910265.735353388</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>162229820</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>162229820.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>60.96</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>60.92</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>62.42</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>62.42</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>18065946.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>24629570.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>24629570</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>33040029.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>41666978.42</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>41666978.42</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-3475027.706523113</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>18065946</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>18065946.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>61.14</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>62.5</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>27824259.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>30390214.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>30390214.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>34185793.5</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>42136243.64</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>42136243.64</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-2740923.705399424</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>27824259</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>27824259.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>60.36</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>58.86</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>60.54</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>60.54</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>77580224.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>79284453.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>79284453.40000001</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>84912840.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>72269039.02</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>72269039.02</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>2807953.910534963</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>77580224</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>77580224.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>59.67999999999999</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>58.78</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>60.5</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>68679719.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>72148960.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>72148960.40000001</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>90110205.8</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>72193962.72</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>72193962.72</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>3240003.762390554</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>68679719</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>68679719.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>59.14000000000001</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>58.76</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>60.48</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>88690818.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>75126830.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>75126830</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>87268579.5</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>72346830.68</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>72346830.68000001</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>4695128.952098861</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>88690818</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>88690818.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>58.67999999999999</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>58.71</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>60.47</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>60.47</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>115567139.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>74144824.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>74144824.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>81784425.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>72084632.36</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>72084632.36</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>4462149.724821508</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>115567139</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>115567139.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>58.78000000000001</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>58.79</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>60.49</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>60.49</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>45904367.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>75212898.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>75212898</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>72514217.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>73305435.6</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>73305435.59999999</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>1090353.945681661</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>45904367</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>45904367.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>59.06</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>58.94</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>60.48</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>41902759.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>90541228.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>90541228.40000001</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>71510331.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>73138507.26</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>73138507.26000001</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>3698430.048850372</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>41902759</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>41902759.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>59.5</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>59.07</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>60.49</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>59.07</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>60.49</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>83569067.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>108071451.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>108071451.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>73551967.7</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>73167175.2</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>73167175.2</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>7720909.980203897</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>83569067</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>83569067.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>59.5</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>59.21</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>60.49</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>60.49</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>83780792.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>99410329.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>99410329</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>72742387.5</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>73230595.74</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>73230595.73999999</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>8727315.811415926</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>83780792</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>83780792.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>59.38</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>59.25</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>60.49</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>60.49</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>120907505.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>89424027.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>89424027</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>68150476.5</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>72428984.18</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>72428984.18000001</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>9830663.755596831</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>120907505</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>120907505.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>59.16</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>60.46</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>59.16</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>60.46</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>122546019.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>69815537.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>69815537.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>58939461.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>71232340.72</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>71232340.72</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>7077917.86315538</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>122546019</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>122546019.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>58.34</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>59.06</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>60.41</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>60.41</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>129553873.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>52479434.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>52479434.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>53076655.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>69459357.48</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>69459357.48</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>2717085.878840625</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>129553873</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>129553873.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>36.41</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>35.32</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>34.47</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>34.47</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>161572231.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>240570769.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>240570769.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>629616498.6</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>206878582.5</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>206878582.5</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-17426575.89810002</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>161572231</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>161572231.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>36.52999999999999</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>35.17</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>34.39</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>34.39</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>197503329.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>278245147.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>278245147.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>646323954.8</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>206671816.56</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>206671816.56</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>2060159.931648731</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>197503329</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>197503329.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>36.9</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>35.04</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>34.34</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>34.34</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>227614543.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>340699756.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>340699756.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>633625870.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>204548060.46</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>204548060.46</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>25975016.33373082</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>227614543</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>227614543.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>37.48999999999999</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>34.86</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>34.28</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>34.28</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>375701443.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>509270392.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>509270392.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>621486122.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>201103506.6</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>201103506.6</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>55985216.25335771</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>375701443</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>375701443.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>38.65</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>34.65</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>34.19</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>34.19</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>240462301.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1026098305.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1026098305.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>606246411.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>194979670.48</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>194979670.48</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>80991004.84377623</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>240462301</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>240462301.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>39.03</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>34.44</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>34.1</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>349944122.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1018662227.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1018662227.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>593517295.1</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>191032278.32</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>191032278.32</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>128310932.1570964</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>349944122</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>349944122.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>38.97000000000001</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>34.03</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>34.26</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>34.03</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>509776373.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1014402762.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1014402762</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>570627652.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>185688546.2</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>185688546.2</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>179598099.9205147</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>509776373</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>509776373.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>38.08</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>34.04</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>33.94</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>1070467723.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>926551983.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>926551983.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>531940288.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>178005860.4</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>178005860.4</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>229326380.5496652</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>1070467723</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1070467723.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>36.85</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>33.73</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>33.82</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>33.82</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>2959841008.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>733701852.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>733701852</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>432411528.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>157810280.4</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>157810280.4</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>232102480.3573924</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>2959841008</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>2959841008.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>34.84</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>33.18</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>33.61</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>33.61</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>203281913.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>186394516.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>186394516.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>144992722.4</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>100231097.78</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>100231097.78</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>25346110.96280992</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>203281913</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>203281913.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>33.54</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>32.81</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>33.48</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>33.48</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>328646793.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>168372362.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>168372362.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>127858482.1</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>97431191.76</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>97431191.76000001</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>24420268.04330602</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>328646793</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>328646793.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
